--- a/docs/qa/Greenfield_Test_Execution_Tracker.xlsx
+++ b/docs/qa/Greenfield_Test_Execution_Tracker.xlsx
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>The Testing gate carries one platform-derived condition</t>
+          <t>The Testing gate carries two platform-derived conditions</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>The merge gate requires the Reviewer role (08 Code Review)</t>
+          <t>The merge gate requires the Tech Lead role (08 Code Review)</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="G163" s="6" t="inlineStr">
         <is>
-          <t>P10 Engineer · a reviewer account</t>
+          <t>P10 Engineer · P5 Tech Lead</t>
         </is>
       </c>
       <c r="H163" s="6" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="G165" s="6" t="inlineStr">
         <is>
-          <t>a reviewer account</t>
+          <t>P5 Tech Lead</t>
         </is>
       </c>
       <c r="H165" s="6" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>/onboarding tells a greenfield project it is brownfield</t>
+          <t>Onboarding is hidden on greenfield, and the screen behind it is still brownfield-only</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
